--- a/Puzzlebobbleゲーム作業シート.xlsx
+++ b/Puzzlebobbleゲーム作業シート.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\2026\puzzleboble\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14FC694B-3461-4A5D-BEDB-C22B22DEB6EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2702BF10-3A2B-4E12-9BB3-34C38E0F7E5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="15264" yWindow="0" windowWidth="15552" windowHeight="16656" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="実装項目" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="194" uniqueCount="135">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="112">
   <si>
     <t>※厳密で無くてよいが、なんとなく他人に伝わることが望ましい。</t>
   </si>
@@ -58,171 +58,24 @@
     <t>移動</t>
   </si>
   <si>
-    <t>HP</t>
-  </si>
-  <si>
     <t>投射物を発射</t>
   </si>
   <si>
     <t>-</t>
   </si>
   <si>
-    <t>前に進む。</t>
-  </si>
-  <si>
-    <t>発動</t>
-  </si>
-  <si>
-    <t>素早く移動する</t>
-  </si>
-  <si>
-    <t>大きい人参</t>
-  </si>
-  <si>
-    <t>大きな人参が落下し、敵を攻撃する。</t>
-  </si>
-  <si>
-    <t>聖水</t>
-  </si>
-  <si>
-    <t>宝箱</t>
-  </si>
-  <si>
-    <t>開く</t>
-  </si>
-  <si>
-    <t>プレイヤーが触れるとアニメーションして開き、スキル選択に遷移する。</t>
-  </si>
-  <si>
-    <t>宝箱の生成</t>
-  </si>
-  <si>
-    <t>一定レベル事に宝箱を生成する。</t>
-  </si>
-  <si>
-    <t>インゲームUI</t>
-  </si>
-  <si>
     <t>レベル</t>
   </si>
   <si>
-    <t>表示</t>
-  </si>
-  <si>
-    <t>現在のレベルを表示する。</t>
-  </si>
-  <si>
     <t>経験値</t>
   </si>
   <si>
-    <t>現在の経験値を表示する。</t>
-  </si>
-  <si>
     <t>経過時間</t>
   </si>
   <si>
-    <t>現在の経過時間を表示する。</t>
-  </si>
-  <si>
-    <t>HP表示</t>
-  </si>
-  <si>
-    <t>現在のHPを表示する。</t>
-  </si>
-  <si>
-    <t>スキル状況</t>
-  </si>
-  <si>
-    <t>アイコン表示</t>
-  </si>
-  <si>
-    <t>獲得スキルのアイコンを表示する。</t>
-  </si>
-  <si>
-    <t>スタック表示</t>
-  </si>
-  <si>
-    <t>獲得スキルのスタック数を表示する。</t>
-  </si>
-  <si>
-    <t>クールタイム表示</t>
-  </si>
-  <si>
-    <t>獲得スキルのクールタイムを表示する。</t>
-  </si>
-  <si>
-    <t>SelectSkillInterfaceController</t>
-  </si>
-  <si>
-    <t>スキル選択画面</t>
-  </si>
-  <si>
-    <t>ポーズ</t>
-  </si>
-  <si>
-    <t>インゲームを一時停止して画面を表示する</t>
-  </si>
-  <si>
-    <t>ポーズ解除</t>
-  </si>
-  <si>
-    <t>インゲームの一時停止を解除して画面を非表示にする。</t>
-  </si>
-  <si>
-    <t>スキルカード</t>
-  </si>
-  <si>
-    <t>抽選</t>
-  </si>
-  <si>
-    <t>表示するスキルカードを抽選する。</t>
-  </si>
-  <si>
-    <t>スキル名表示</t>
-  </si>
-  <si>
-    <t>スキル名を表示する。</t>
-  </si>
-  <si>
-    <t>スキルアイコン表示</t>
-  </si>
-  <si>
-    <t>スキルアイコンを表示する。</t>
-  </si>
-  <si>
-    <t>スキルレベル表示</t>
-  </si>
-  <si>
-    <t>現在のスキルレベルと入手後のスキルレベルを表示する。</t>
-  </si>
-  <si>
-    <t>GameOverInterfaceController</t>
-  </si>
-  <si>
-    <t>新記録</t>
-  </si>
-  <si>
-    <t>新記録表示</t>
-  </si>
-  <si>
-    <t>新記録ならNEW RECORDと表示する。</t>
-  </si>
-  <si>
     <t>駆除した数</t>
   </si>
   <si>
-    <t>駆除した数表示</t>
-  </si>
-  <si>
-    <t>駆除した蜂の数を表示する。</t>
-  </si>
-  <si>
-    <t>取得スキル</t>
-  </si>
-  <si>
-    <t>スキルレベルを表示する。</t>
-  </si>
-  <si>
     <t>※参考に用意したが、個人で作る場合には別段無くても困らないと思う。</t>
   </si>
   <si>
@@ -380,22 +233,6 @@
   </si>
   <si>
     <t>クールタイムの現在値</t>
-  </si>
-  <si>
-    <t>ボトルが落ちてきて聖水をだす、その範囲に入ればダメージ。</t>
-    <rPh sb="4" eb="5">
-      <t>オ</t>
-    </rPh>
-    <rPh sb="9" eb="11">
-      <t>セイスイ</t>
-    </rPh>
-    <rPh sb="17" eb="19">
-      <t>ハンイ</t>
-    </rPh>
-    <rPh sb="20" eb="21">
-      <t>ハイ</t>
-    </rPh>
-    <phoneticPr fontId="4"/>
   </si>
   <si>
     <t>右、左の方向キーで大砲の方向を変更できる。</t>
@@ -466,22 +303,6 @@
   </si>
   <si>
     <t>ステージ表示</t>
-    <phoneticPr fontId="4"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>ステージを表示？</t>
-    </r>
-    <rPh sb="5" eb="7">
-      <t>ヒョウジ</t>
-    </rPh>
     <phoneticPr fontId="4"/>
   </si>
   <si>
@@ -560,6 +381,271 @@
     <t>到着</t>
     <rPh sb="0" eb="2">
       <t>トウチャク</t>
+    </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>大砲が向いている方向に向かって打つ</t>
+    <rPh sb="0" eb="2">
+      <t>タイホウ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>ム</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>ホウコウ</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>ム</t>
+    </rPh>
+    <rPh sb="15" eb="16">
+      <t>ウ</t>
+    </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>天井 or ボールに当たった時停止する</t>
+    <rPh sb="0" eb="2">
+      <t>テンジョウ</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>ア</t>
+    </rPh>
+    <rPh sb="14" eb="15">
+      <t>トキ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>テイシ</t>
+    </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>次のボールをセット</t>
+    <rPh sb="0" eb="1">
+      <t>ツギ</t>
+    </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>到着した場合次のボールをセット</t>
+    <rPh sb="0" eb="2">
+      <t>トウチャク</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>バアイ</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>ツギ</t>
+    </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>グリッドのデータ保持</t>
+    <rPh sb="8" eb="10">
+      <t>ホジ</t>
+    </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>座標の管理方法</t>
+    <rPh sb="0" eb="2">
+      <t>ザヒョウ</t>
+    </rPh>
+    <rPh sb="3" eb="7">
+      <t>カンリホウホウ</t>
+    </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>ボールをどの位置に移動させるか表示させる</t>
+    <rPh sb="6" eb="8">
+      <t>イチ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>イドウ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t xml:space="preserve">ステージを表示Lv1 ~ </t>
+    <rPh sb="5" eb="7">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t xml:space="preserve">ステージを表示Lv10 ~ </t>
+    <rPh sb="5" eb="7">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t xml:space="preserve">ステージを表示Lv20 ~ </t>
+    <rPh sb="5" eb="7">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>色を入れる</t>
+    <rPh sb="0" eb="1">
+      <t>イロ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>イ</t>
+    </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>ボールの色を複数用意</t>
+    <rPh sb="4" eb="5">
+      <t>イロ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>フクスウ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>ヨウイ</t>
+    </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>合体時、消える</t>
+    <rPh sb="0" eb="3">
+      <t>ガッタイジ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>キ</t>
+    </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>ボールが3つ集まったとききれいに消える</t>
+    <rPh sb="6" eb="7">
+      <t>アツ</t>
+    </rPh>
+    <rPh sb="16" eb="17">
+      <t>キ</t>
+    </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>浮いているボールを落とす</t>
+    <rPh sb="0" eb="1">
+      <t>ウ</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>オ</t>
+    </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>ボールが消えた時天井やボールに触れていないボールがあった場合消える</t>
+    <rPh sb="4" eb="5">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>トキ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>テンジョウ</t>
+    </rPh>
+    <rPh sb="15" eb="16">
+      <t>フ</t>
+    </rPh>
+    <rPh sb="28" eb="30">
+      <t>バアイ</t>
+    </rPh>
+    <rPh sb="30" eb="31">
+      <t>キ</t>
+    </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>ボール同士でぶつかると</t>
+    <rPh sb="3" eb="5">
+      <t>ドウシ</t>
+    </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>ボール同士引っ付く</t>
+    <rPh sb="3" eb="5">
+      <t>ドウシ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>ヒ</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>ツ</t>
+    </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>ボールをステージに用意</t>
+    <rPh sb="9" eb="11">
+      <t>ヨウイ</t>
+    </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>ボールをステージに</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>ステージ内に用意</t>
+    <rPh sb="4" eb="5">
+      <t>ナイ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>ヨウイ</t>
+    </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>アニメーション</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>大砲</t>
+    <rPh sb="0" eb="2">
+      <t>タイホウ</t>
+    </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>ボール</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>ネクストボール</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>ボールが落ちる</t>
+    <rPh sb="4" eb="5">
+      <t>オ</t>
+    </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>天井</t>
+    <rPh sb="0" eb="2">
+      <t>テンジョウ</t>
+    </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>上から天井がせまる</t>
+    <rPh sb="0" eb="1">
+      <t>ウエ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>テンジョウ</t>
     </rPh>
     <phoneticPr fontId="4"/>
   </si>
@@ -674,16 +760,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -693,6 +776,8 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -957,462 +1042,294 @@
       <c r="A5" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B5" s="10" t="s">
-        <v>124</v>
-      </c>
-      <c r="C5" s="10" t="s">
-        <v>121</v>
+      <c r="B5" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="C5" s="9" t="s">
+        <v>71</v>
       </c>
       <c r="D5" s="5" t="b">
         <v>0</v>
       </c>
-      <c r="E5" s="11" t="s">
-        <v>127</v>
-      </c>
-      <c r="F5" s="13" t="s">
-        <v>132</v>
+      <c r="E5" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="F5" s="12" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="10" t="s">
-        <v>125</v>
-      </c>
-      <c r="C6" s="11" t="s">
-        <v>123</v>
+      <c r="B6" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="C6" s="10" t="s">
+        <v>73</v>
       </c>
       <c r="D6" s="5" t="b">
         <v>0</v>
       </c>
-      <c r="E6" s="11" t="s">
-        <v>128</v>
-      </c>
-      <c r="F6" s="13" t="s">
-        <v>133</v>
+      <c r="E6" s="10" t="s">
+        <v>78</v>
+      </c>
+      <c r="F6" s="12" t="s">
+        <v>82</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B7" s="12" t="s">
-        <v>126</v>
-      </c>
-      <c r="C7" s="10" t="s">
-        <v>122</v>
+      <c r="B7" s="11" t="s">
+        <v>76</v>
+      </c>
+      <c r="C7" s="9" t="s">
+        <v>72</v>
       </c>
       <c r="D7" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="E7" s="10" t="s">
+        <v>79</v>
+      </c>
+      <c r="F7" s="13" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D8" s="5" t="b">
         <v>0</v>
       </c>
-      <c r="E7" s="11" t="s">
-        <v>129</v>
-      </c>
-      <c r="F7" s="13" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C8" s="2" t="s">
+      <c r="F8" s="13" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D9" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="F9" s="13" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C10" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="D8" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F8" s="8" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D9" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F9" s="8" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C10" s="8" t="s">
-        <v>131</v>
-      </c>
-      <c r="D10" s="5" t="b">
-        <v>0</v>
+      <c r="D10" s="1" t="b">
+        <v>1</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="F10" s="2" t="s">
-        <v>13</v>
+      <c r="F10" s="7" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D11" s="1"/>
-      <c r="E11" s="9" t="s">
-        <v>134</v>
-      </c>
-      <c r="F11" s="2"/>
+      <c r="D11" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F11" s="7" t="s">
+        <v>70</v>
+      </c>
     </row>
     <row r="12" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B12" s="2"/>
-      <c r="C12" s="8"/>
-      <c r="D12" s="8"/>
-      <c r="E12" s="8"/>
-      <c r="F12" s="8"/>
-      <c r="G12" s="8"/>
+      <c r="C12" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="D12" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F12" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="G12" s="7"/>
     </row>
     <row r="13" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B13" s="2"/>
-      <c r="C13" s="2"/>
-      <c r="D13" s="2"/>
-      <c r="E13" s="2"/>
-      <c r="F13" s="2"/>
+      <c r="D13" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="E13" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="F13" s="8" t="s">
+        <v>85</v>
+      </c>
     </row>
     <row r="14" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B14" s="2"/>
+      <c r="C14" s="7"/>
+      <c r="D14" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="E14" s="7" t="s">
+        <v>86</v>
+      </c>
+      <c r="F14" s="7" t="s">
+        <v>87</v>
+      </c>
     </row>
     <row r="15" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B15" s="2"/>
-      <c r="C15" s="2" t="s">
-        <v>12</v>
-      </c>
       <c r="D15" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="E15" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="F15" s="2" t="s">
-        <v>15</v>
+        <v>1</v>
+      </c>
+      <c r="E15" s="14" t="s">
+        <v>94</v>
+      </c>
+      <c r="F15" s="10" t="s">
+        <v>95</v>
       </c>
     </row>
     <row r="16" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B16" s="2"/>
-      <c r="C16" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D16" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="E16" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="F16" s="2" t="s">
-        <v>17</v>
+      <c r="D16" s="14" t="b">
+        <v>1</v>
+      </c>
+      <c r="E16" s="10" t="s">
+        <v>96</v>
+      </c>
+      <c r="F16" s="10" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="17" spans="1:7" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B17" s="4"/>
-      <c r="C17" s="4" t="s">
-        <v>18</v>
-      </c>
       <c r="D17" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="E17" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="F17" s="8" t="s">
-        <v>118</v>
+        <v>1</v>
+      </c>
+      <c r="E17" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="F17" s="10" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="18" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B18" s="2"/>
-      <c r="C18" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="D18" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="E18" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="F18" s="2" t="s">
-        <v>21</v>
+      <c r="D18" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="E18" s="10" t="s">
+        <v>100</v>
+      </c>
+      <c r="F18" s="10" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="19" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B19" s="2"/>
-      <c r="C19" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D19" s="2" t="b">
+      <c r="C19" s="10" t="s">
+        <v>102</v>
+      </c>
+      <c r="D19" s="5" t="b">
         <v>0</v>
       </c>
-      <c r="E19" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="F19" s="2" t="s">
-        <v>23</v>
+      <c r="E19" s="10" t="s">
+        <v>103</v>
+      </c>
+      <c r="F19" s="10" t="s">
+        <v>104</v>
       </c>
     </row>
     <row r="20" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="2" t="s">
-        <v>24</v>
-      </c>
+      <c r="A20" s="2"/>
       <c r="B20" s="2"/>
-      <c r="C20" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="D20" s="2" t="b">
+      <c r="D20" s="5" t="b">
         <v>0</v>
       </c>
-      <c r="E20" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="F20" s="2" t="s">
-        <v>27</v>
+      <c r="E20" s="10" t="s">
+        <v>110</v>
+      </c>
+      <c r="F20" s="10" t="s">
+        <v>111</v>
       </c>
     </row>
     <row r="21" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C21" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="D21" s="2" t="b">
+      <c r="C21" s="9" t="s">
+        <v>105</v>
+      </c>
+      <c r="D21" s="5" t="b">
         <v>0</v>
       </c>
-      <c r="E21" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="F21" s="2" t="s">
-        <v>29</v>
+      <c r="E21" s="10" t="s">
+        <v>106</v>
       </c>
     </row>
     <row r="22" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C22" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="D22" s="2" t="b">
+      <c r="D22" s="5" t="b">
         <v>0</v>
       </c>
-      <c r="E22" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="F22" s="2" t="s">
-        <v>31</v>
+      <c r="E22" s="10" t="s">
+        <v>107</v>
       </c>
     </row>
     <row r="23" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C23" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D23" s="2" t="b">
+      <c r="D23" s="5" t="b">
         <v>0</v>
       </c>
-      <c r="E23" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="F23" s="2" t="s">
-        <v>33</v>
+      <c r="E23" s="10" t="s">
+        <v>108</v>
       </c>
     </row>
     <row r="24" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C24" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="D24" s="2" t="b">
+      <c r="D24" s="5" t="b">
         <v>0</v>
       </c>
-      <c r="E24" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="F24" s="2" t="s">
-        <v>36</v>
+      <c r="E24" s="10" t="s">
+        <v>109</v>
       </c>
     </row>
     <row r="25" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D25" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="E25" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="F25" s="2" t="s">
-        <v>38</v>
+      <c r="C25" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="D25" s="14" t="b">
+        <v>1</v>
+      </c>
+      <c r="E25" s="8" t="s">
+        <v>89</v>
+      </c>
+      <c r="F25" s="8" t="s">
+        <v>90</v>
       </c>
     </row>
     <row r="26" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D26" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="E26" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="F26" s="2" t="s">
-        <v>40</v>
-      </c>
       <c r="G26" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="27" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="2"/>
-      <c r="B27" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="C27" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="D27" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="E27" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="F27" s="2" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D28" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="E28" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="F28" s="5" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C29" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="D29" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="E29" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="F29" s="2" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D30" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="E30" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="F30" s="2" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D31" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="E31" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="F31" s="2" t="s">
-        <v>53</v>
-      </c>
-    </row>
+    </row>
+    <row r="28" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="29" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="30" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="31" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="32" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="33" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="34" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D34" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="E34" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="F34" s="2" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="34" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="35" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="2"/>
-      <c r="B35" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="C35" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="D35" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="E35" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="F35" s="2" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D36" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="E36" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="F36" s="5" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C37" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="D37" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="E37" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="F37" s="2" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C38" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="D38" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="E38" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="F38" s="2" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C39" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="D39" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="E39" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="F39" s="2" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D40" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="E40" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="F40" s="2" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="42" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="43" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="44" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="45" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="46" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="47" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="48" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    </row>
+    <row r="36" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="37" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="38" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="39" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="40" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="41" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="42" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="43" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="44" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="45" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="46" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="47" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="48" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="49" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="50" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="51" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -2390,27 +2307,27 @@
   <sheetData>
     <row r="1" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
-        <v>65</v>
+        <v>16</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="3" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>66</v>
+        <v>17</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>67</v>
+        <v>18</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>6</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>68</v>
+        <v>19</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>69</v>
+        <v>20</v>
       </c>
       <c r="E4" s="3" t="s">
         <v>6</v>
@@ -2418,106 +2335,106 @@
     </row>
     <row r="5" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>70</v>
+        <v>21</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>71</v>
+        <v>22</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>72</v>
+        <v>23</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>73</v>
+        <v>24</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>74</v>
+        <v>25</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C6" s="2" t="s">
-        <v>75</v>
+        <v>26</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>73</v>
+        <v>24</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>76</v>
+        <v>27</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C7" s="2" t="s">
-        <v>77</v>
+        <v>28</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>78</v>
+        <v>29</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>79</v>
+        <v>30</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C8" s="2" t="s">
-        <v>80</v>
+        <v>31</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>81</v>
+        <v>32</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>82</v>
+        <v>33</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C9" s="2" t="s">
-        <v>83</v>
+        <v>34</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>81</v>
+        <v>32</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>84</v>
+        <v>35</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C10" s="2" t="s">
-        <v>85</v>
+        <v>36</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>73</v>
+        <v>24</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>86</v>
+        <v>37</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C11" s="2" t="s">
-        <v>87</v>
+        <v>38</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>88</v>
+        <v>39</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>89</v>
+        <v>40</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="13" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="14" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>90</v>
+        <v>41</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
-        <v>67</v>
+        <v>18</v>
       </c>
       <c r="B15" s="3" t="s">
         <v>6</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>68</v>
+        <v>19</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>69</v>
+        <v>20</v>
       </c>
       <c r="E15" s="3" t="s">
         <v>6</v>
@@ -2525,223 +2442,223 @@
     </row>
     <row r="16" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>91</v>
+        <v>42</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>92</v>
+        <v>43</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>93</v>
+        <v>44</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>73</v>
+        <v>24</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>25</v>
+        <v>12</v>
       </c>
     </row>
     <row r="17" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C17" s="2" t="s">
-        <v>94</v>
+        <v>45</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>73</v>
+        <v>24</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>28</v>
+        <v>13</v>
       </c>
     </row>
     <row r="18" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C18" s="2" t="s">
-        <v>95</v>
+        <v>46</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>73</v>
+        <v>24</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>96</v>
+        <v>47</v>
       </c>
     </row>
     <row r="19" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C19" s="2" t="s">
-        <v>97</v>
+        <v>48</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>88</v>
+        <v>39</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>30</v>
+        <v>14</v>
       </c>
     </row>
     <row r="20" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C20" s="2" t="s">
-        <v>98</v>
+        <v>49</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>99</v>
+        <v>50</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>100</v>
+        <v>51</v>
       </c>
     </row>
     <row r="21" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C21" s="2" t="s">
-        <v>101</v>
+        <v>52</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>73</v>
+        <v>24</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>102</v>
+        <v>53</v>
       </c>
     </row>
     <row r="22" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C22" s="2" t="s">
-        <v>103</v>
+        <v>54</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>73</v>
+        <v>24</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>104</v>
+        <v>55</v>
       </c>
     </row>
     <row r="23" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C23" s="2" t="s">
-        <v>105</v>
+        <v>56</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>73</v>
+        <v>24</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>60</v>
+        <v>15</v>
       </c>
     </row>
     <row r="24" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C24" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="D24" s="7" t="s">
-        <v>107</v>
+        <v>57</v>
+      </c>
+      <c r="D24" s="6" t="s">
+        <v>58</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>108</v>
+        <v>59</v>
       </c>
     </row>
     <row r="25" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>109</v>
+        <v>60</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>110</v>
+        <v>61</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>111</v>
+        <v>62</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>73</v>
+        <v>24</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>112</v>
+        <v>63</v>
       </c>
     </row>
     <row r="26" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C26" s="2" t="s">
-        <v>75</v>
+        <v>26</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>73</v>
+        <v>24</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>76</v>
+        <v>27</v>
       </c>
     </row>
     <row r="27" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C27" s="2" t="s">
-        <v>77</v>
+        <v>28</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>78</v>
+        <v>29</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>79</v>
+        <v>30</v>
       </c>
     </row>
     <row r="28" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C28" s="2" t="s">
-        <v>80</v>
+        <v>31</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>81</v>
+        <v>32</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>82</v>
+        <v>33</v>
       </c>
     </row>
     <row r="29" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C29" s="2" t="s">
-        <v>83</v>
+        <v>34</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>81</v>
+        <v>32</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>84</v>
+        <v>35</v>
       </c>
     </row>
     <row r="30" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C30" s="2" t="s">
-        <v>93</v>
+        <v>44</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>73</v>
+        <v>24</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>25</v>
+        <v>12</v>
       </c>
     </row>
     <row r="31" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C31" s="2" t="s">
-        <v>85</v>
+        <v>36</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>73</v>
+        <v>24</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>86</v>
+        <v>37</v>
       </c>
     </row>
     <row r="32" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C32" s="2" t="s">
-        <v>113</v>
+        <v>64</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>73</v>
+        <v>24</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>114</v>
+        <v>65</v>
       </c>
     </row>
     <row r="33" spans="3:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C33" s="2" t="s">
-        <v>115</v>
+        <v>66</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>88</v>
+        <v>39</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>89</v>
+        <v>40</v>
       </c>
     </row>
     <row r="34" spans="3:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C34" s="2" t="s">
-        <v>116</v>
+        <v>67</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>88</v>
+        <v>39</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>117</v>
+        <v>68</v>
       </c>
     </row>
     <row r="35" spans="3:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
